--- a/Result/profitability/8099.xlsx
+++ b/Result/profitability/8099.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6900000000000001</v>
+        <v>0.7312500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>23.15625</v>
+        <v>22.9625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.69375</v>
+        <v>0.6925</v>
       </c>
       <c r="N3" t="n">
-        <v>23.26625</v>
+        <v>22.88125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6787500000000001</v>
+        <v>0.7212500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>23.13125</v>
+        <v>22.89</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.74375</v>
       </c>
       <c r="N5" t="n">
-        <v>23.10375</v>
+        <v>23.0925</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.70375</v>
+        <v>0.715</v>
       </c>
       <c r="N6" t="n">
-        <v>23.2675</v>
+        <v>24.00125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6675</v>
+        <v>0.6412500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>24.4575</v>
+        <v>24.515</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0.6237499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>24.6075</v>
+        <v>24.2725</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8099</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E75" t="n">
+        <v>307</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>102</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>106</v>
+      </c>
+      <c r="K75" t="n">
+        <v>79</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6837500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.965</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1060546102097348</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6458333333333335</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.003968253968253954</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
